--- a/summary_report.xlsx
+++ b/summary_report.xlsx
@@ -489,7 +489,7 @@
         <v>59.09090909090909</v>
       </c>
       <c r="E2" t="n">
-        <v>97.08234466672275</v>
+        <v>97.08233534203404</v>
       </c>
       <c r="F2" t="n">
         <v>3</v>
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1970823.446667227</v>
+        <v>1970823.35342034</v>
       </c>
       <c r="J2" t="n">
-        <v>970823.4466672274</v>
+        <v>970823.3534203405</v>
       </c>
       <c r="K2" t="n">
-        <v>56366.99139672238</v>
+        <v>56366.98959484799</v>
       </c>
     </row>
     <row r="3">
@@ -530,7 +530,7 @@
         <v>59.25925925925925</v>
       </c>
       <c r="E3" t="n">
-        <v>76.7022594038572</v>
+        <v>76.70220168158933</v>
       </c>
       <c r="F3" t="n">
         <v>2.5</v>
@@ -546,13 +546,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1767022.594038572</v>
+        <v>1767022.016815893</v>
       </c>
       <c r="J3" t="n">
-        <v>767022.5940385719</v>
+        <v>767022.0168158934</v>
       </c>
       <c r="K3" t="n">
-        <v>74389.01387665658</v>
+        <v>74389.00217521904</v>
       </c>
     </row>
     <row r="4">
@@ -571,7 +571,7 @@
         <v>62.5</v>
       </c>
       <c r="E4" t="n">
-        <v>59.87377431014098</v>
+        <v>59.87371606579844</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1598737.74310141</v>
+        <v>1598737.160657984</v>
       </c>
       <c r="J4" t="n">
-        <v>598737.7431014099</v>
+        <v>598737.1606579844</v>
       </c>
       <c r="K4" t="n">
-        <v>41527.73434486792</v>
+        <v>41527.72261851742</v>
       </c>
     </row>
     <row r="5">
@@ -612,7 +612,7 @@
         <v>66.66666666666666</v>
       </c>
       <c r="E5" t="n">
-        <v>38.46196247818089</v>
+        <v>38.46198023492224</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1384619.624781809</v>
+        <v>1384619.802349222</v>
       </c>
       <c r="J5" t="n">
-        <v>384619.6247818088</v>
+        <v>384619.8023492224</v>
       </c>
       <c r="K5" t="n">
-        <v>21129.95852640879</v>
+        <v>21129.95685482697</v>
       </c>
     </row>
     <row r="6">
@@ -653,7 +653,7 @@
         <v>55.55555555555556</v>
       </c>
       <c r="E6" t="n">
-        <v>38.20006315091974</v>
+        <v>38.20006605738117</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1382000.631509197</v>
+        <v>1382000.660573812</v>
       </c>
       <c r="J6" t="n">
-        <v>382000.6315091974</v>
+        <v>382000.6605738117</v>
       </c>
       <c r="K6" t="n">
-        <v>18266.8790059359</v>
+        <v>18266.87927233734</v>
       </c>
     </row>
     <row r="7">
@@ -694,7 +694,7 @@
         <v>50</v>
       </c>
       <c r="E7" t="n">
-        <v>16.77028517598319</v>
+        <v>16.77029066978923</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1167702.851759832</v>
+        <v>1167702.906697892</v>
       </c>
       <c r="J7" t="n">
-        <v>167702.8517598319</v>
+        <v>167702.9066978924</v>
       </c>
       <c r="K7" t="n">
-        <v>12931.60975526324</v>
+        <v>12931.61056433475</v>
       </c>
     </row>
     <row r="8">
@@ -729,20 +729,20 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46153846153847</v>
+        <v>41.66666666666667</v>
       </c>
       <c r="E8" t="n">
-        <v>11.04330255878021</v>
+        <v>7.632384347261604</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -751,13 +751,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1110433.025587802</v>
+        <v>1076323.843472616</v>
       </c>
       <c r="J8" t="n">
-        <v>110433.0255878021</v>
+        <v>76323.84347261605</v>
       </c>
       <c r="K8" t="n">
-        <v>26116.18054161494</v>
+        <v>25396.53393832815</v>
       </c>
     </row>
     <row r="9">
@@ -776,7 +776,7 @@
         <v>42.85714285714285</v>
       </c>
       <c r="E9" t="n">
-        <v>7.612015055460088</v>
+        <v>6.930271831709751</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -792,13 +792,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1076120.150554601</v>
+        <v>1069302.718317098</v>
       </c>
       <c r="J9" t="n">
-        <v>76120.15055460087</v>
+        <v>69302.71831709752</v>
       </c>
       <c r="K9" t="n">
-        <v>29308.54019465601</v>
+        <v>29261.49262969942</v>
       </c>
     </row>
     <row r="10">
@@ -817,7 +817,7 @@
         <v>42.85714285714285</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.802726560579659</v>
+        <v>-2.802701754742849</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>971972.7343942034</v>
+        <v>971972.9824525715</v>
       </c>
       <c r="J10" t="n">
-        <v>-28027.26560579659</v>
+        <v>-28027.01754742849</v>
       </c>
       <c r="K10" t="n">
-        <v>29095.98258296405</v>
+        <v>29095.98746484961</v>
       </c>
     </row>
     <row r="11">
@@ -858,7 +858,7 @@
         <v>45</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.72652522360934</v>
+        <v>-7.765932132351189</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>922734.7477639066</v>
+        <v>922340.6786764881</v>
       </c>
       <c r="J11" t="n">
-        <v>-77265.25223609339</v>
+        <v>-77659.32132351189</v>
       </c>
       <c r="K11" t="n">
-        <v>37173.69778268137</v>
+        <v>37159.7744613738</v>
       </c>
     </row>
   </sheetData>
